--- a/Team-Data/2014-15/1-4-2014-15.xlsx
+++ b/Team-Data/2014-15/1-4-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>4.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>3</v>
@@ -751,16 +818,16 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -769,13 +836,13 @@
         <v>8</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -784,22 +851,22 @@
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -927,10 +994,10 @@
         <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
         <v>7</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -978,13 +1045,13 @@
         <v>25</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,25 +1110,25 @@
         <v>36.5</v>
       </c>
       <c r="J4" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
         <v>7.1</v>
       </c>
       <c r="M4" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O4" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="P4" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0.745</v>
@@ -1070,16 +1137,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W4" t="n">
         <v>7.3</v>
@@ -1088,61 +1155,61 @@
         <v>4.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>20.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>-1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="n">
         <v>15</v>
       </c>
-      <c r="AG4" t="n">
-        <v>17</v>
-      </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>17</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1154,19 +1221,19 @@
         <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY4" t="n">
         <v>13</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>14</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
@@ -1175,7 +1242,7 @@
         <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -1285,22 +1352,22 @@
         <v>-4.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
         <v>12</v>
@@ -1330,25 +1397,25 @@
         <v>24</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
         <v>6</v>
@@ -1479,7 +1546,7 @@
         <v>6</v>
       </c>
       <c r="AH6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
         <v>19</v>
@@ -1494,7 +1561,7 @@
         <v>13</v>
       </c>
       <c r="AM6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN6" t="n">
         <v>12</v>
@@ -1509,10 +1576,10 @@
         <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>4</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -1571,58 +1638,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
         <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="H7" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J7" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.453</v>
+        <v>0.455</v>
       </c>
       <c r="L7" t="n">
         <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="N7" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O7" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P7" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R7" t="n">
         <v>10.7</v>
       </c>
       <c r="S7" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T7" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V7" t="n">
         <v>13.7</v>
@@ -1631,31 +1698,31 @@
         <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA7" t="n">
         <v>21.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.9</v>
+        <v>101.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -1670,25 +1737,25 @@
         <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
         <v>12</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>17</v>
@@ -1697,7 +1764,7 @@
         <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -1709,10 +1776,10 @@
         <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -1756,64 +1823,64 @@
         <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.735</v>
+        <v>0.706</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="J8" t="n">
         <v>86.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.48</v>
+        <v>0.478</v>
       </c>
       <c r="L8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O8" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P8" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="S8" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
         <v>12.3</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
@@ -1822,25 +1889,25 @@
         <v>20.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>110.1</v>
+        <v>109.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
         <v>16</v>
@@ -1861,25 +1928,25 @@
         <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
         <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
         <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1888,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF9" t="n">
         <v>19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>19</v>
@@ -2031,7 +2098,7 @@
         <v>15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
         <v>25</v>
@@ -2046,7 +2113,7 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP9" t="n">
         <v>4</v>
@@ -2064,16 +2131,16 @@
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
         <v>30</v>
@@ -2082,13 +2149,13 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
         <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.303</v>
+        <v>0.281</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>36.3</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.425</v>
+        <v>0.422</v>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M10" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O10" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P10" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.676</v>
+        <v>0.674</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S10" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
       <c r="T10" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U10" t="n">
         <v>20.7</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
         <v>7.4</v>
@@ -2183,25 +2250,25 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>96.5</v>
+        <v>96</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
         <v>27</v>
@@ -2210,10 +2277,10 @@
         <v>13</v>
       </c>
       <c r="AI10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
@@ -2231,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2240,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
         <v>5</v>
@@ -2258,7 +2325,7 @@
         <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>10</v>
@@ -2267,10 +2334,10 @@
         <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2462,7 @@
         <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83</v>
+        <v>82.7</v>
       </c>
       <c r="K12" t="n">
         <v>0.431</v>
@@ -2508,22 +2575,22 @@
         <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.7</v>
+        <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.707</v>
+        <v>0.706</v>
       </c>
       <c r="R12" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S12" t="n">
         <v>31.9</v>
@@ -2532,37 +2599,37 @@
         <v>44.3</v>
       </c>
       <c r="U12" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X12" t="n">
         <v>4.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
@@ -2571,16 +2638,16 @@
         <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI12" t="n">
         <v>28</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2604,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,22 +2686,22 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
         <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -2663,40 +2730,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.371</v>
+        <v>0.382</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J13" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K13" t="n">
-        <v>0.43</v>
+        <v>0.432</v>
       </c>
       <c r="L13" t="n">
         <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="O13" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P13" t="n">
         <v>20.6</v>
@@ -2705,19 +2772,19 @@
         <v>0.736</v>
       </c>
       <c r="R13" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S13" t="n">
         <v>34.1</v>
       </c>
       <c r="T13" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="U13" t="n">
         <v>20.8</v>
       </c>
       <c r="V13" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W13" t="n">
         <v>5.7</v>
@@ -2726,7 +2793,7 @@
         <v>4.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z13" t="n">
         <v>20.9</v>
@@ -2735,13 +2802,13 @@
         <v>20.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>-1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>21</v>
@@ -2756,13 +2823,13 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>13</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>19</v>
@@ -2771,10 +2838,10 @@
         <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
         <v>26</v>
@@ -2783,10 +2850,10 @@
         <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -2801,13 +2868,13 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>8</v>
@@ -2935,7 +3002,7 @@
         <v>9</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>10</v>
@@ -2959,19 +3026,19 @@
         <v>7</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
         <v>14</v>
       </c>
       <c r="AT14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
@@ -2983,7 +3050,7 @@
         <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -3030,13 +3097,13 @@
         <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.303</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
@@ -3045,34 +3112,34 @@
         <v>38.3</v>
       </c>
       <c r="J15" t="n">
-        <v>86.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L15" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M15" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="N15" t="n">
         <v>0.363</v>
       </c>
       <c r="O15" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.748</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="T15" t="n">
         <v>42.5</v>
@@ -3084,7 +3151,7 @@
         <v>12.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X15" t="n">
         <v>4.9</v>
@@ -3093,37 +3160,37 @@
         <v>4.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF15" t="n">
         <v>24</v>
       </c>
-      <c r="AF15" t="n">
-        <v>22</v>
-      </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK15" t="n">
         <v>23</v>
@@ -3135,28 +3202,28 @@
         <v>21</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
         <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV15" t="n">
         <v>6</v>
@@ -3171,10 +3238,10 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BB15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
@@ -3332,7 +3399,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3344,25 +3411,25 @@
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY16" t="n">
         <v>23</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>24</v>
       </c>
       <c r="AZ16" t="n">
         <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
         <v>15</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -3391,34 +3458,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.429</v>
+        <v>0.412</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J17" t="n">
-        <v>74</v>
+        <v>74.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.464</v>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M17" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="N17" t="n">
         <v>0.355</v>
@@ -3427,7 +3494,7 @@
         <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.73</v>
@@ -3436,10 +3503,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="T17" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="U17" t="n">
         <v>19.8</v>
@@ -3451,7 +3518,7 @@
         <v>8.5</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
         <v>4.3</v>
@@ -3463,22 +3530,22 @@
         <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>-4.1</v>
+        <v>-4.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
         <v>29</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL17" t="n">
         <v>14</v>
@@ -3502,7 +3569,7 @@
         <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3523,13 +3590,13 @@
         <v>28</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>7</v>
       </c>
       <c r="AX17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3538,10 +3605,10 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
         <v>24</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -3573,61 +3640,61 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
         <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
       </c>
       <c r="I18" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J18" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.462</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O18" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P18" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.777</v>
       </c>
       <c r="R18" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U18" t="n">
         <v>22.9</v>
       </c>
       <c r="V18" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="W18" t="n">
         <v>9</v>
@@ -3636,7 +3703,7 @@
         <v>4.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z18" t="n">
         <v>22.7</v>
@@ -3645,46 +3712,46 @@
         <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
       </c>
       <c r="AF18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG18" t="n">
         <v>15</v>
       </c>
-      <c r="AG18" t="n">
-        <v>14</v>
-      </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ18" t="n">
         <v>22</v>
       </c>
       <c r="AK18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>25</v>
@@ -3699,7 +3766,7 @@
         <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>9</v>
@@ -3714,7 +3781,7 @@
         <v>20</v>
       </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>26</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3933,7 @@
         <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3902,7 +3969,7 @@
         <v>16</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -3937,130 +4004,130 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J20" t="n">
-        <v>84.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.766</v>
+        <v>0.754</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>19.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AB20" t="n">
         <v>101.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
         <v>18</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>19</v>
       </c>
       <c r="AT20" t="n">
         <v>12</v>
@@ -4069,13 +4136,13 @@
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>26</v>
@@ -4084,13 +4151,13 @@
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>13</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>0.139</v>
+        <v>0.143</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="J21" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K21" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N21" t="n">
         <v>0.353</v>
       </c>
       <c r="O21" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0.783</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
         <v>28.6</v>
       </c>
       <c r="T21" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="U21" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W21" t="n">
         <v>7.3</v>
@@ -4185,19 +4252,19 @@
         <v>3.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA21" t="n">
         <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.6</v>
+        <v>-7.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4212,7 +4279,7 @@
         <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ21" t="n">
         <v>20</v>
@@ -4221,7 +4288,7 @@
         <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM21" t="n">
         <v>22</v>
@@ -4239,7 +4306,7 @@
         <v>4</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4251,10 +4318,10 @@
         <v>15</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
         <v>28</v>
@@ -4266,7 +4333,7 @@
         <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -4379,13 +4446,13 @@
         <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
         <v>15</v>
@@ -4418,7 +4485,7 @@
         <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR22" t="n">
         <v>5</v>
@@ -4439,7 +4506,7 @@
         <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>11</v>
@@ -4448,13 +4515,13 @@
         <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -4483,82 +4550,82 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>0.361</v>
+        <v>0.351</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J23" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.374</v>
       </c>
       <c r="O23" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="P23" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
         <v>19.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4567,10 +4634,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
@@ -4582,16 +4649,16 @@
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4603,37 +4670,37 @@
         <v>26</v>
       </c>
       <c r="AR23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
         <v>22</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -4761,13 +4828,13 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4779,13 +4846,13 @@
         <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4812,7 +4879,7 @@
         <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -4847,88 +4914,88 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>0.556</v>
+        <v>0.543</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.8</v>
+        <v>39.5</v>
       </c>
       <c r="J25" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.464</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M25" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O25" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P25" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="R25" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T25" t="n">
         <v>42.2</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V25" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
         <v>3.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB25" t="n">
-        <v>107.2</v>
+        <v>106.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>13</v>
@@ -4946,10 +5013,10 @@
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
@@ -4973,34 +5040,34 @@
         <v>20</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
         <v>23</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>7</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
         <v>6</v>
@@ -5131,7 +5198,7 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
@@ -5149,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5182,7 +5249,7 @@
         <v>6</v>
       </c>
       <c r="BC26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
         <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.412</v>
+        <v>0.424</v>
       </c>
       <c r="H27" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I27" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L27" t="n">
         <v>5.2</v>
@@ -5241,76 +5308,76 @@
         <v>15.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.338</v>
+        <v>0.343</v>
       </c>
       <c r="O27" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="P27" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.774</v>
       </c>
       <c r="R27" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S27" t="n">
         <v>33.4</v>
       </c>
       <c r="T27" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V27" t="n">
         <v>16.5</v>
       </c>
       <c r="W27" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="AA27" t="n">
         <v>25.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>102</v>
+        <v>102.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF27" t="n">
         <v>18</v>
       </c>
       <c r="AG27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH27" t="n">
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,7 +5398,7 @@
         <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>7</v>
@@ -5340,7 +5407,7 @@
         <v>8</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
@@ -5361,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -5393,70 +5460,70 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.588</v>
+        <v>0.6</v>
       </c>
       <c r="H28" t="n">
         <v>49.3</v>
       </c>
       <c r="I28" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.468</v>
       </c>
       <c r="L28" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.366</v>
+        <v>0.371</v>
       </c>
       <c r="O28" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="T28" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
         <v>19.5</v>
@@ -5471,7 +5538,7 @@
         <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5489,10 +5556,10 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>10</v>
@@ -5501,22 +5568,22 @@
         <v>15</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
@@ -5525,13 +5592,13 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5543,10 +5610,10 @@
         <v>21</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>0.706</v>
+        <v>0.727</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
@@ -5593,7 +5660,7 @@
         <v>39.4</v>
       </c>
       <c r="J29" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.462</v>
@@ -5605,67 +5672,67 @@
         <v>24.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O29" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P29" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R29" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S29" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T29" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U29" t="n">
         <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="W29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X29" t="n">
         <v>4.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z29" t="n">
         <v>21.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="AC29" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>5</v>
@@ -5674,7 +5741,7 @@
         <v>9</v>
       </c>
       <c r="AK29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5683,13 +5750,13 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
@@ -5704,10 +5771,10 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW29" t="n">
         <v>16</v>
@@ -5719,16 +5786,16 @@
         <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>3</v>
       </c>
       <c r="BC29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5856,10 +5923,10 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM30" t="n">
         <v>20</v>
@@ -5868,19 +5935,19 @@
         <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP30" t="n">
         <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5889,13 +5956,13 @@
         <v>23</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -5907,10 +5974,10 @@
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF31" t="n">
         <v>9</v>
@@ -6029,13 +6096,13 @@
         <v>10</v>
       </c>
       <c r="AH31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI31" t="n">
         <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>4</v>
@@ -6071,7 +6138,7 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
         <v>13</v>
@@ -6083,7 +6150,7 @@
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
         <v>17</v>
@@ -6092,7 +6159,7 @@
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-4-2014-15</t>
+          <t>2015-01-04</t>
         </is>
       </c>
     </row>
